--- a/artfynd/A 45291-2025 artfynd.xlsx
+++ b/artfynd/A 45291-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000804</v>
       </c>
       <c r="B2" t="n">
-        <v>97528</v>
+        <v>97533</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 45291-2025 artfynd.xlsx
+++ b/artfynd/A 45291-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000804</v>
       </c>
       <c r="B2" t="n">
-        <v>97533</v>
+        <v>97536</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 45291-2025 artfynd.xlsx
+++ b/artfynd/A 45291-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000804</v>
       </c>
       <c r="B2" t="n">
-        <v>97536</v>
+        <v>97546</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 45291-2025 artfynd.xlsx
+++ b/artfynd/A 45291-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000804</v>
       </c>
       <c r="B2" t="n">
-        <v>97546</v>
+        <v>97553</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 45291-2025 artfynd.xlsx
+++ b/artfynd/A 45291-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000804</v>
       </c>
       <c r="B2" t="n">
-        <v>97553</v>
+        <v>97555</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 45291-2025 artfynd.xlsx
+++ b/artfynd/A 45291-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000804</v>
       </c>
       <c r="B2" t="n">
-        <v>97555</v>
+        <v>97581</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 45291-2025 artfynd.xlsx
+++ b/artfynd/A 45291-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000804</v>
       </c>
       <c r="B2" t="n">
-        <v>97581</v>
+        <v>97582</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 45291-2025 artfynd.xlsx
+++ b/artfynd/A 45291-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000804</v>
       </c>
       <c r="B2" t="n">
-        <v>97582</v>
+        <v>97583</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 45291-2025 artfynd.xlsx
+++ b/artfynd/A 45291-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000804</v>
       </c>
       <c r="B2" t="n">
-        <v>97583</v>
+        <v>97587</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 45291-2025 artfynd.xlsx
+++ b/artfynd/A 45291-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000804</v>
       </c>
       <c r="B2" t="n">
-        <v>97587</v>
+        <v>97589</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 45291-2025 artfynd.xlsx
+++ b/artfynd/A 45291-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000804</v>
       </c>
       <c r="B2" t="n">
-        <v>97589</v>
+        <v>97593</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 45291-2025 artfynd.xlsx
+++ b/artfynd/A 45291-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000804</v>
       </c>
       <c r="B2" t="n">
-        <v>97593</v>
+        <v>97601</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 45291-2025 artfynd.xlsx
+++ b/artfynd/A 45291-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129000804</v>
       </c>
       <c r="B2" t="n">
-        <v>97601</v>
+        <v>97604</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
